--- a/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (3) (2).xlsx
+++ b/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (3) (2).xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,9 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -98,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -119,6 +122,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -692,10 +698,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
+            <rPr/>
             <t xml:space="preserve">SHOPID -&gt; STOREID
 DISCOUNT -&gt; Discount
 USERID -&gt; SalesRepID
@@ -705,18 +708,23 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id (1000097205)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> -&gt; DistributorID
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> (</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">) -&gt; DistributorID
 PRODUCT_CODE -&gt; ProductID  (strip leading letters)
 SUPPLIER_ID -&gt; WarehouseID
 SALE_ORDER_ID -&gt; OrderNumber
@@ -729,20 +737,25 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency (KES)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> -&gt; Currency
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.currency</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> (</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>KES</t>
+          </r>
+          <r>
+            <rPr/>
+            <t>) -&gt; Currency
 QUANTITY -&gt; QuantityInvoiced
-VALUE_SOLD -&gt; AmountInvoiced
+VALUE_SOLD -&gt; AmountInvoiced  (PAPI amount2, 2 decimals, format 0.00)
 ENTRY_TYPE -&gt; TransType</t>
           </r>
         </is>
@@ -753,7 +766,7 @@
 from {database}.bi_salesmaster as a
 left join {database}.bi_customer_visits as b on a.VisitID = b.visitid
 inner join {database}.bi_products as c on a.PRODUCT_ID = c.id and c.supplier = '{supplier}'
-where a.Created_AT between '&lt;fromDate&gt; 00:00:00' and '&lt;toDate&gt; 00:00:00'
+where a.Created_AT between '&lt;fromDate&gt; 00:00:00' and '&lt;toDate&gt; 23:59:59'
 order by a.Entry_ID desc
 LIMIT &lt;pageSize + 1&gt; OFFSET &lt;pageNumber * pageSize&gt;</t>
         </is>
@@ -792,7 +805,7 @@
           </r>
           <r>
             <rPr/>
-            <t>, VAT 2 decimals, ProductID numeric, InvoiceStatus from DELIVERED</t>
+            <t>, VAT and AmountInvoiced 2 decimals, ProductID numeric, InvoiceStatus from DELIVERED, toDate 23:59:59</t>
           </r>
         </is>
       </c>
@@ -871,19 +884,26 @@
       <c r="C3" s="3" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
+            <rPr/>
             <t xml:space="preserve"> {
             "StoreID": 1801,
             "SalesRepID": 89,
             "RouteID": "",
             "ProductID": "969584",
-            "DistributorID": "???",
+            "DistributorID": </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>"1000097205"</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">,
             "WarehouseID": 183,
             "OrderNumber": 69,
-            "OrderDate": "",
+            "OrderDate": "10/09/2026",
             "OrderStartTime": "",
             "OrderEndTime": "",
             "OrderStatus": "Cancelled",
@@ -892,20 +912,15 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
+              <b val="1"/>
             </rPr>
             <t>"KES"</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
+            <rPr/>
             <t>,
             "QuantityOrdered": 1,
-            "AmountOrdered": 372,
+            "AmountOrdered": "372.00",
             "Discount": 0,
             "VATAmount": "51.31"
         }</t>
@@ -915,18 +930,35 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
+            <rPr/>
             <t xml:space="preserve">SHOP_ID -&gt; StoreID
 USER_ID -&gt; SalesRepID  (not SALES_REP name)
 ROUTEID -&gt; RouteID
 PRODUCT_CODE -&gt; ProductID  (strip leading letters)
-hardcoded '???' -&gt; DistributorID
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> (</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">) -&gt; DistributorID
 SUPPLIER_ID -&gt; WarehouseID
 ENTRY_ID -&gt; OrderNumber
-CHECKINTIME -&gt; OrderDate  (dd/MM/yyyy)
+ENTRY_TIME -&gt; OrderDate  (dd/MM/yyyy)
 CHECKINTIME -&gt; OrderStartTime  (HH:mm:ss)
 CHECKOUTTIME -&gt; OrderEndTime  (HH:mm:ss)
 DELIVERED -&gt; OrderStatus
@@ -935,20 +967,25 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency (KES)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> -&gt; Currency
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.currency</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> (</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>KES</t>
+          </r>
+          <r>
+            <rPr/>
+            <t>) -&gt; Currency
 QUANTITY -&gt; QuantityOrdered
-TOTAL_VAT_INC -&gt; AmountOrdered
+TOTAL_VAT_INC -&gt; AmountOrdered  (PAPI amount2, 2 decimals)
 DISCOUNT -&gt; Discount
 TOTAL_VAT -&gt; VATAmount  (PAPI amount2, 2 decimals)</t>
           </r>
@@ -960,9 +997,9 @@
 from {database}.bi_ordersmaster as a
 inner join {database}.bi_products as c on a.PRODUCT_ID = c.id and c.supplier = '{supplier}'
 left join {database}.bi_customer_visits as b on a.VISIT_ID = b.visitid
+where a.ENTRY_TIME between '&lt;fromDate&gt; 00:00:00' and '&lt;toDate&gt; 23:59:59'
 order by a.ENTRY_ID desc
-LIMIT &lt;pageSize + 1&gt; OFFSET &lt;pageNumber * pageSize&gt;
-Note: Exp/PAPI still send fromDate and toDate. Current SAPI Order SQL does not filter on those dates.</t>
+LIMIT &lt;pageSize + 1&gt; OFFSET &lt;pageNumber * pageSize&gt;</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -987,7 +1024,20 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>UPDATED — SalesRepID = USER_ID, ProductID numeric, VAT 2 decimals</t>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">UPDATED — SalesRepID = USER_ID, OrderDate from ENTRY_TIME, DistributorID </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
+          <r>
+            <rPr/>
+            <t>, AmountOrdered 2 decimals, date filter on ENTRY_TIME</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1403,7 +1453,7 @@
             "StoreCategory": "RETAIL SHOP",
             "Channel": "GENERAL TRADE",
             "StoreClassification": "GENERAL TRADE",
-            "WarehouseID": "???",
+            "WarehouseID": null,
             "Longitude": 36.9328219,
             "Latitude": -1.2349905,
             "City": "RUIRU",
@@ -1422,7 +1472,7 @@
 CUSTOMERCATEGORY -&gt; StoreCategory
 CHANNEL -&gt; Channel
 CHANNEL -&gt; StoreClassification
-hardcoded '???' -&gt; WarehouseID
+null -&gt; WarehouseID
 LONGITUDE -&gt; Longitude
 LATITUDE -&gt; Latitude
 LOCATIONNAME -&gt; City
@@ -1438,6 +1488,7 @@
           <t>Select a.*
 from {database}.bi_customer_master as a
 where a.Customer_Type = 'Customer'
+and a.DATECREATED between '&lt;fromDate&gt; 00:00:00' and '&lt;toDate&gt; 23:59:59'
 and exists (
   Select 1 from (
     Select distinct SHOPID from (
@@ -1451,8 +1502,7 @@
   where w.SHOPID = a.SHOPID
 )
 order by a.SHOPID
-LIMIT &lt;pageSize + 1&gt; OFFSET &lt;pageNumber * pageSize&gt;
-Note: Exp/PAPI send fromDate and toDate. Current SAPI Customer SQL does not filter on those dates.</t>
+LIMIT &lt;pageSize + 1&gt; OFFSET &lt;pageNumber * pageSize&gt;</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1477,7 +1527,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Unchanged mapping</t>
+          <t>UPDATED — WarehouseID null, DATECREATED date filter</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1557,7 @@
             "DistributorWarehouseCode": "",
             "Date": "17/08/2026",
             "InventoryQuantity": -880,
-            "InventoryPrice": 1060
+            "InventoryPrice": null
         }</t>
         </is>
       </c>
@@ -1518,7 +1568,7 @@
 stockpoint_name -&gt; DistributorWarehouseCode
 date_created -&gt; Date  (dd/MM/yyyy)
 quantity -&gt; InventoryQuantity  (goodsin minus goodsout)
-total_cost -&gt; InventoryPrice</t>
+null -&gt; InventoryPrice</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1560,7 +1610,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>UPDATED — quantity = goodsin minus goodsout</t>
+          <t>UPDATED — quantity = goodsin minus goodsout, InventoryPrice null</t>
         </is>
       </c>
     </row>
@@ -1623,18 +1673,54 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> {
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> {
             "WarehouseID": 183,
             "WarehouseName": "GIKAMBURA STOCKPOINT",
-            "DistributorID": ""
+            "DistributorID": </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>"1000097205"</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">
         }</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>ID -&gt; WarehouseID
+          <r>
+            <rPr/>
+            <t xml:space="preserve">ID -&gt; WarehouseID
 CUSTOMERNAME -&gt; WarehouseName
-'' -&gt; DistributorID</t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> (</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
+          <r>
+            <rPr/>
+            <t>) -&gt; DistributorID</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1672,7 +1758,20 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Unchanged mapping. EXISTS still commented.</t>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">UPDATED — DistributorID </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
+          <r>
+            <rPr/>
+            <t>. EXISTS still commented.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2160,7 +2259,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>amount2 format 0.00</t>
         </is>
       </c>
     </row>
@@ -2285,14 +2384,38 @@
           <t>DistributorID</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>hardcoded</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>'???' still in PAPI DWL</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">property </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> = </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2353,7 +2476,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>CHECKINTIME</t>
+          <t>ENTRY_TIME</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2548,7 +2671,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>amount2 format 0.00</t>
         </is>
       </c>
     </row>
@@ -3061,14 +3184,10 @@
           <t>WarehouseID</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>hardcoded</t>
-        </is>
-      </c>
+      <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>'???' still in PAPI DWL</t>
+          <t>null</t>
         </is>
       </c>
     </row>
@@ -3361,14 +3480,10 @@
           <t>InventoryPrice</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>total_cost</t>
-        </is>
-      </c>
+      <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>null</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3542,38 @@
           <t>DistributorID</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>empty</t>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr/>
+            <t xml:space="preserve">property </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>papi.sat.solutech.distributor.id</t>
+          </r>
+          <r>
+            <rPr/>
+            <t xml:space="preserve"> = </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>1000097205</t>
+          </r>
         </is>
       </c>
     </row>

--- a/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (3) (2).xlsx
+++ b/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (3) (2).xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="1" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Payloads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Current field map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Query parameters" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Authentication" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payloads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current field map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query parameters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Authentication" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Payloads'!$A$1:$J$9</definedName>
@@ -637,94 +637,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> {
-            "STOREID": 1714,
+          <t>{
+            "StoreID": 2151,
             "Discount": 0,
-            "SalesRepID": 75,
-            "VATAmount": "247.47",
-            "RouteID": 42,
-            "DistributorID": </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>"1000097205"</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">,
-            "ProductID": "903017",
-            "WarehouseID": 0,
-            "OrderNumber": "",
-            "InvoiceNumber": 1640,
-            "InvoiceDate": "13/08/2026",
-            "InvoiceTime": "16:11:25",
+            "SalesRepID": 112,
+            "VATAmount": "49.04",
+            "RouteID": "",
+            "DistributorID": "1000097205",
+            "ProductID": "0238167",
+            "WarehouseID": 1925,
+            "OrderNumber": 286,
+            "InvoiceNumber": 2901,
+            "InvoiceDate": "25/09/2026",
+            "InvoiceTime": "15:15:36",
             "InvoiceStatus": "Delivered",
-            "UnitOfMeasure": "CARD",
-            "Currency": </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>"KES"</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>,
-            "QuantityInvoiced": 1,
-            "AmountInvoiced": 1794.17,
+            "UnitOfMeasure": "PIECE",
+            "Currency": "KES",
+            "QuantityInvoiced": 12,
+            "AmountInvoiced": "355.56",
             "TransType": "Sale"
-        }</t>
-          </r>
+}</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">SHOPID -&gt; STOREID
+          <t>SHOPID -&gt; StoreID
 DISCOUNT -&gt; Discount
 USERID -&gt; SalesRepID
 TOTAL_VAT -&gt; VATAmount  (PAPI amount2, 2 decimals, format 0.00)
 ROUTEID -&gt; RouteID
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> (</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">) -&gt; DistributorID
+papi.sat.solutech.distributor.id (1000097205) -&gt; DistributorID
 PRODUCT_CODE -&gt; ProductID  (strip leading letters)
 SUPPLIER_ID -&gt; WarehouseID
 SALE_ORDER_ID -&gt; OrderNumber
@@ -733,31 +675,10 @@
 CREATED_AT -&gt; InvoiceTime  (HH:mm:ss)
 DELIVERED -&gt; InvoiceStatus
 PACKAGING -&gt; UnitOfMeasure
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> (</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>KES</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>) -&gt; Currency
+papi.sat.solutech.currency (KES) -&gt; Currency
 QUANTITY -&gt; QuantityInvoiced
 VALUE_SOLD -&gt; AmountInvoiced  (PAPI amount2, 2 decimals, format 0.00)
 ENTRY_TYPE -&gt; TransType</t>
-          </r>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -793,20 +714,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">UPDATED — DistributorID </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>, VAT and AmountInvoiced 2 decimals, ProductID numeric, InvoiceStatus from DELIVERED, toDate 23:59:59</t>
-          </r>
+          <t>UPDATED — DistributorID 1000097205, VAT and AmountInvoiced 2 decimals, ProductID numeric, InvoiceStatus from DELIVERED, toDate 23:59:59</t>
         </is>
       </c>
     </row>
@@ -883,79 +791,34 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> {
-            "StoreID": 1801,
-            "SalesRepID": 89,
-            "RouteID": "",
-            "ProductID": "969584",
-            "DistributorID": </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"1000097205"</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">,
-            "WarehouseID": 183,
-            "OrderNumber": 69,
-            "OrderDate": "10/09/2026",
-            "OrderStartTime": "",
-            "OrderEndTime": "",
-            "OrderStatus": "Cancelled",
-            "UnitOfMeasure": "PACKET",
-            "Currency": </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"KES"</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>,
-            "QuantityOrdered": 1,
-            "AmountOrdered": "372.00",
+          <t>{
+            "StoreID": 2814,
+            "SalesRepID": 103,
+            "RouteID": 115,
+            "ProductID": "3109556",
+            "DistributorID": "1000097205",
+            "WarehouseID": 2166,
+            "OrderNumber": 366,
+            "OrderDate": "25/09/2026",
+            "OrderStartTime": "17:42:38",
+            "OrderEndTime": "18:12:59",
+            "OrderStatus": "Open",
+            "UnitOfMeasure": "PIECE",
+            "Currency": "KES",
+            "QuantityOrdered": 6,
+            "AmountOrdered": "1104.00",
             "Discount": 0,
-            "VATAmount": "51.31"
-        }</t>
-          </r>
+            "VATAmount": "152.28"
+}</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">SHOP_ID -&gt; StoreID
+          <t>SHOP_ID -&gt; StoreID
 USER_ID -&gt; SalesRepID  (not SALES_REP name)
 ROUTEID -&gt; RouteID
 PRODUCT_CODE -&gt; ProductID  (strip leading letters)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> (</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">) -&gt; DistributorID
+papi.sat.solutech.distributor.id (1000097205) -&gt; DistributorID
 SUPPLIER_ID -&gt; WarehouseID
 ENTRY_ID -&gt; OrderNumber
 ENTRY_TIME -&gt; OrderDate  (dd/MM/yyyy)
@@ -963,32 +826,11 @@
 CHECKOUTTIME -&gt; OrderEndTime  (HH:mm:ss)
 DELIVERED -&gt; OrderStatus
 PACKAGING -&gt; UnitOfMeasure
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> (</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>KES</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>) -&gt; Currency
+papi.sat.solutech.currency (KES) -&gt; Currency
 QUANTITY -&gt; QuantityOrdered
 TOTAL_VAT_INC -&gt; AmountOrdered  (PAPI amount2, 2 decimals)
 DISCOUNT -&gt; Discount
 TOTAL_VAT -&gt; VATAmount  (PAPI amount2, 2 decimals)</t>
-          </r>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1024,20 +866,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">UPDATED — SalesRepID = USER_ID, OrderDate from ENTRY_TIME, DistributorID </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>, AmountOrdered 2 decimals, date filter on ENTRY_TIME</t>
-          </r>
+          <t>UPDATED — SalesRepID = USER_ID, OrderDate from ENTRY_TIME, DistributorID 1000097205, AmountOrdered 2 decimals, date filter on ENTRY_TIME</t>
         </is>
       </c>
     </row>
@@ -1073,18 +902,18 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> {
-            "ProductID": "502418",
-            "ProductSKU": "CRISTAL MED BLU BX 25 BCL KE",
-            "UnitofMeasure": "PACKET"
-        }</t>
+          <t>{
+            "ProductID": "3268896",
+            "ProductSKU": "AWICK FRESHMATIC ROSE  + GADGET SEEDING PRICE 250ML (4)",
+            "UnitOfMeasure": "PIECE"
+}</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>productcode -&gt; ProductID  (strip leading letters)
 product_desc -&gt; ProductSKU
-uomname -&gt; UnitofMeasure
+uomname -&gt; UnitOfMeasure
 PAPI returns only these three fields.</t>
         </is>
       </c>
@@ -1156,13 +985,13 @@
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>{
-            "RouteID": 31,
-            "RouteName": "DICKSON NJUE MONDAY",
-            "SalesRepID": 75,
+            "RouteID": 110,
+            "RouteName": "MOSES RB TUESDAY",
+            "SalesRepID": 110,
             "RouteType": "Weekly",
             "SalesRepType": "Van Sales",
-            "Date": "15/06/2026"
-        }</t>
+            "Date": "07/09/2026"
+}</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1264,64 +1093,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">{
-            "SalesRepID": 72,
-            "SalesRepName": "ESTHER KAGIRI",
-            "DistributorID": </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>"1000097205"</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>,
+          <t>{
+            "SalesRepID": 100,
+            "SalesRepName": "ISAAC MUGE",
+            "DistributorID": "1000097205",
             "WarehouseID": 183,
-            "SalesRepType": "Drivers (Delivery Agents)"
-        }</t>
-          </r>
+            "SalesRepType": "Admin"
+}</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">id -&gt; SalesRepID
+          <t>id -&gt; SalesRepID
 name -&gt; SalesRepName
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id (1000097205)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> -&gt; DistributorID
+papi.sat.solutech.distributor.id (1000097205) -&gt; DistributorID
 STOCKPOINT_ID -&gt; WarehouseID  (from bi_stockpoint_allocation join; not warehouse_code)
 saler_category -&gt; SalesRepType</t>
-          </r>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1375,16 +1162,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">UPDATED — STOCKPOINT_ID join, DistributorID </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
+          <t>UPDATED — STOCKPOINT_ID join, DistributorID 1000097205</t>
         </is>
       </c>
     </row>
@@ -1448,21 +1226,21 @@
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>{
-            "StoreID": 199,
-            "StoreName": "MANDELA SHOP",
-            "StoreCategory": "RETAIL SHOP",
+            "StoreID": 1980,
+            "StoreName": "ONE ZERO ONE SELFRIGES",
+            "StoreCategory": "SHOP AND BROWSER",
             "Channel": "GENERAL TRADE",
             "StoreClassification": "GENERAL TRADE",
             "WarehouseID": null,
-            "Longitude": 36.9328219,
-            "Latitude": -1.2349905,
-            "City": "RUIRU",
-            "Region": "NAIROBI",
+            "Longitude": 37.5852265,
+            "Latitude": 0.3526255,
+            "City": "MERU",
+            "Region": "MOUNTAIN",
             "County": "",
             "StoreStatus": 1,
-            "StoreCreationDate": "15/06/2026",
+            "StoreCreationDate": "10/09/2026",
             "StoreSize": ""
-        }</t>
+}</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1552,19 +1330,19 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>{
-            "ProductSKU": "969584",
-            "UnitofMeasure": "PACKET",
-            "DistributorWarehouseCode": "",
-            "Date": "17/08/2026",
-            "InventoryQuantity": -880,
+            "ProductID": "3300090",
+            "UnitOfMeasure": "PIECE",
+            "DistributorWarehouseCode": "EMBU STOCKPOINT",
+            "Date": "22/09/2026",
+            "InventoryQuantity": 21,
             "InventoryPrice": null
-        }</t>
+}</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>productcode -&gt; ProductSKU  (strip leading letters)
-uomname -&gt; UnitofMeasure
+          <t>productcode -&gt; ProductID  (strip leading letters)
+uomname -&gt; UnitOfMeasure
 stockpoint_name -&gt; DistributorWarehouseCode
 date_created -&gt; Date  (dd/MM/yyyy)
 quantity -&gt; InventoryQuantity  (goodsin minus goodsout)
@@ -1673,54 +1451,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> {
+          <t>{
             "WarehouseID": 183,
             "WarehouseName": "GIKAMBURA STOCKPOINT",
-            "DistributorID": </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"1000097205"</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">
-        }</t>
-          </r>
+            "DistributorID": "1000097205"
+}</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">ID -&gt; WarehouseID
+          <t>ID -&gt; WarehouseID
 CUSTOMERNAME -&gt; WarehouseName
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> (</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>) -&gt; DistributorID</t>
-          </r>
+papi.sat.solutech.distributor.id (1000097205) -&gt; DistributorID</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1758,20 +1500,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">UPDATED — DistributorID </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
-          <r>
-            <rPr/>
-            <t>. EXISTS still commented.</t>
-          </r>
+          <t>UPDATED — DistributorID 1000097205. EXISTS still commented.</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1554,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>STOREID</t>
+          <t>StoreID</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1940,48 +1669,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
+          <t>papi.sat.solutech.distributor.id</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
+          <t>property papi.sat.solutech.distributor.id = 1000097205</t>
         </is>
       </c>
     </row>
@@ -2174,48 +1867,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
+          <t>papi.sat.solutech.currency</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>KES</t>
-          </r>
+          <t>property papi.sat.solutech.currency = KES</t>
         </is>
       </c>
     </row>
@@ -2386,36 +2043,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
+          <t>papi.sat.solutech.distributor.id</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
+          <t>property papi.sat.solutech.distributor.id = 1000097205</t>
         </is>
       </c>
     </row>
@@ -2586,48 +2219,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
+          <t>papi.sat.solutech.currency</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.currency</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>KES</t>
-          </r>
+          <t>property papi.sat.solutech.currency = KES</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2368,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>UnitofMeasure</t>
+          <t>UnitOfMeasure</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2974,48 +2571,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
+          <t>papi.sat.solutech.distributor.id</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
+          <t>property papi.sat.solutech.distributor.id = 1000097205</t>
         </is>
       </c>
     </row>
@@ -3367,7 +2928,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>ProductSKU</t>
+          <t>ProductID</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3389,7 +2950,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>UnitofMeasure</t>
+          <t>UnitOfMeasure</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3544,36 +3105,12 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
+          <t>papi.sat.solutech.distributor.id</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr/>
-            <t xml:space="preserve">property </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>papi.sat.solutech.distributor.id</t>
-          </r>
-          <r>
-            <rPr/>
-            <t xml:space="preserve"> = </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>1000097205</t>
-          </r>
+          <t>property papi.sat.solutech.distributor.id = 1000097205</t>
         </is>
       </c>
     </row>
@@ -3659,58 +3196,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -3742,36 +3228,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3260,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -3835,58 +3292,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -3918,36 +3324,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3356,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4011,58 +3388,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4094,36 +3420,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +3452,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4187,58 +3484,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4270,36 +3516,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -4331,7 +3548,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4363,58 +3580,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4446,36 +3612,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -4507,7 +3644,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4539,58 +3676,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4622,36 +3708,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -4683,7 +3740,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4715,58 +3772,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4798,36 +3804,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -4859,7 +3836,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -4891,58 +3868,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Clients never send </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Exp injects them from the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>JWT appid map</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t>.</t>
-          </r>
+          <t>Clients never send database or supplier. Exp injects them from the JWT appid map.</t>
         </is>
       </c>
     </row>
@@ -4974,36 +3900,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>supplier</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> required. pageNumber is a string when forwarded to SAPI.</t>
-          </r>
+          <t>database and supplier required. pageNumber is a string when forwarded to SAPI.</t>
         </is>
       </c>
     </row>
@@ -5035,7 +3932,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 10000.</t>
+          <t>database = MySQL schema. supplier = products.supplier. pageNumber 0-based. page size 2000.</t>
         </is>
       </c>
     </row>
@@ -5110,43 +4007,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Azure AD client_credentials. Token URL https://login.microsoftonline.com/f4faf003-d90b-4832-9df8-c8a22d29bdd4/oauth2/v2.0/token. Scope https://graph.microsoft.com/.default. Kenya client id </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>de772600-0d1f-4492-90b0-a57fcc284cf9</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. Autodiscovery </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>api.id=2850714</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> on flow exp-sat-datashare-api-main (exp-sat-datashare-sand-api).</t>
-          </r>
+          <t>Azure AD client_credentials. Token URL https://login.microsoftonline.com/f4faf003-d90b-4832-9df8-c8a22d29bdd4/oauth2/v2.0/token. Scope https://graph.microsoft.com/.default. Kenya client id de772600-0d1f-4492-90b0-a57fcc284cf9. Autodiscovery api.id=2850714 on flow exp-sat-datashare-api-main (exp-sat-datashare-sand-api).</t>
         </is>
       </c>
     </row>
@@ -5173,28 +4034,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Exp still decodes JWT appid/azp and maps to </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>exp.sat.oidc.&lt;country&gt;.database</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> and .supplier. Secret is not stored in the API.</t>
-          </r>
+          <t>Exp still decodes JWT appid/azp and maps to exp.sat.oidc.&lt;country&gt;.database and .supplier. Secret is not stored in the API.</t>
         </is>
       </c>
     </row>
@@ -5221,88 +4061,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">kenya -&gt; </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>sat_nobleoutlook</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> / </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>RECKITT BENCKISER</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">. libya </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>sat_salvogrima</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">, malta </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>sat_sgmalta</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">, uganda </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>sat_sgug</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> (client ids TBD).</t>
-          </r>
+          <t>kenya -&gt; sat_nobleoutlook / RECKITT BENCKISER. libya sat_salvogrima, malta sat_sgmalta, uganda sat_sgug (client ids TBD).</t>
         </is>
       </c>
     </row>
